--- a/forms/trg/Formulir_TRG_albiorg.xlsx
+++ b/forms/trg/Formulir_TRG_albiorg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B37)</f>
+        <f>COUNTA(Anggota!B5:B38)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F37)</f>
+        <f>COUNTA(Anggota!F5:F38)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,41 +913,33 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Kurniati Umrah Nur, M.AppSc(ME)Hons</t>
+          <t>Dr. rer. nat. Elmi Nurhaidah Zainuddin, DES.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Aquatic Animal Nutrition</t>
+          <t>Algal Biotechnology || Marine Natural Products || Marine and Fisheries Biotechnology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-6177-7495</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/profile</t>
+          <t>5985702</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57201781421</t>
+          <t>19338150100</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Nunun Ainun Putri Sari Banun Kaliky, S.Si., M.Si.</t>
+          <t>Kurniati Umrah Nur, M.AppSc(ME)Hons</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,20 +969,28 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Fish Nutrition and Aquaculture</t>
+          <t>Aquatic Animal Nutrition</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-6177-7495</t>
+        </is>
+      </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6774560</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="n"/>
+          <t>https://sinta.kemdiktisaintek.go.id/profile</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>57201781421</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ir. Edison Saade, M.Sc, Ph.D</t>
+          <t>Nunun Ainun Putri Sari Banun Kaliky, S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>fish nutritionfish, aquaculturechemical, biochemia</t>
+          <t>Fish Nutrition and Aquaculture</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1028,14 +1028,10 @@
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6679646</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>https://www.scopus.com/gateway/author-curation-api/orcid/authorize/authorprofile/57205321816</t>
-        </is>
-      </c>
+          <t>6774560</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1048,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>DR. Marlina Achmad, S.Pi. M.Si</t>
+          <t>Ir. Edison Saade, M.Sc, Ph.D</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1063,26 +1059,22 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Biotechnology and Aquaculture</t>
+          <t>fish nutritionfish, aquaculturechemical, biochemia</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>my-orcid?orcid=0000-0002-8863-8476</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>https://sinta.kemdikbud.go.id/profile#</t>
+          <t>6679646</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57216853679</t>
+          <t>https://www.scopus.com/gateway/author-curation-api/orcid/authorize/authorprofile/57205321816</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1097,12 +1089,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Asmi Citra Malina, S.Pi., M.Agr., Ph.D</t>
+          <t>DR. Marlina Achmad, S.Pi. M.Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1112,7 +1104,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Biotechnology and Aquaculture</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1121,17 +1113,17 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8967-210X</t>
+          <t>my-orcid?orcid=0000-0002-8863-8476</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6006000</t>
+          <t>https://sinta.kemdikbud.go.id/profile#</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>8332256500</t>
+          <t>57216853679</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1146,12 +1138,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Syahrul S.Pi., M.Si.</t>
+          <t>Asmi Citra Malina, S.Pi., M.Agr., Ph.D</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1161,16 +1153,28 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Food Technology/Functional Food</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-8967-210X</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>6006000</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>8332256500</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1183,22 +1187,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Kit Wayne Chew</t>
+          <t>Dr. Syahrul S.Pi., M.Si.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Nanyang Technological University</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Bioprocessing || Biorefinery || Food processing || Microalgae technology || Sustainability</t>
+          <t>Food Technology/Functional Food</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1207,11 +1211,7 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>57192980692</t>
-        </is>
-      </c>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1224,22 +1224,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Awalina, M.Si.</t>
+          <t>Dr. Kit Wayne Chew</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Badan Riset Inovasi Nasional (BRIN)</t>
+          <t>Nanyang Technological University</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Microalgae for Metal Biosorption and Karbon</t>
+          <t>Bioprocessing || Biorefinery || Food processing || Microalgae technology || Sustainability</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1247,14 +1247,10 @@
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>6748639</t>
-        </is>
-      </c>
+      <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/gateway/author-curation-api/orcid/authorize/authorprofile/57200257281</t>
+          <t>57192980692</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1269,12 +1265,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ellya Sinurat, S.Si.</t>
+          <t>Dr. Awalina, M.Si.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1284,26 +1280,22 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Food Technology/Functional Food</t>
+          <t>Microalgae for Metal Biosorption and Karbon</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-6825-7230</t>
-        </is>
-      </c>
+      <c r="J13" s="12" t="n"/>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>https://sinta.kemdikbud.go.id/authors?q=ellya+sinurat</t>
+          <t>6748639</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>57192089799</t>
+          <t>https://www.scopus.com/gateway/author-curation-api/orcid/authorize/authorprofile/57200257281</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1318,31 +1310,43 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Huyyirnah, SP., MP.</t>
+          <t>Dr. Ellya Sinurat, S.Si.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Badan Riset Inovasi Nasional (BRIN)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Biotechnology and Microbiology</t>
+          <t>Food Technology/Functional Food</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-6825-7230</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdikbud.go.id/authors?q=ellya+sinurat</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>57192089799</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1355,12 +1359,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Ariansyah, S.Si., M.Si.</t>
+          <t>Huyyirnah, SP., MP.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1370,7 +1374,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Pharmacology of natural materials</t>
+          <t>Biotechnology and Microbiology</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1392,20 +1396,24 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Dea Pramita, S.Pi.</t>
+          <t>Ariansyah, S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="n"/>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Pharmacology of natural materials</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1425,12 +1433,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Bau Wenni Astuti Dg Egi, S.Pi.</t>
+          <t>Dea Pramita, S.Pi.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1458,12 +1466,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Nur Ainun Makmur, S.Pi.</t>
+          <t>Bau Wenni Astuti Dg Egi, S.Pi.</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1491,12 +1499,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Sri Rahayu, S.Kel.</t>
+          <t>Nur Ainun Makmur, S.Pi.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1524,12 +1532,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Muh. Reyza Dwi Anugrah</t>
+          <t>Sri Rahayu, S.Kel.</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1557,12 +1565,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Akbar Hamzah</t>
+          <t>Muh. Reyza Dwi Anugrah</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1590,12 +1598,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Irfan</t>
+          <t>Muhammad Akbar Hamzah</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1623,12 +1631,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Kasmiati STP, MP, Ph.D.</t>
+          <t>Muhammad Irfan</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1638,7 +1646,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Fishery product technology</t>
+          <t>Our research group is dedicated to advancing algal biotechnology , exploring its potential for sustainable solutions in biofuels, pharmaceuticals, environmental remediation, and more. Through innovative research and interdisciplinary collaboration, we strive to harness the power of algae to address global challenges and drive scientific breakthroughs in biotechnology.</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -1646,16 +1654,8 @@
       <c r="H23" s="12" t="n"/>
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="12" t="n"/>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>6679664</t>
-        </is>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>57201354036</t>
-        </is>
-      </c>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
       <c r="M23" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1668,41 +1668,37 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Mufti Hatur Rahmi, S.Tr.Pi., M.Si.</t>
+          <t>Kasmiati STP, MP, Ph.D.</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Aquatic Product Technology</t>
+          <t>Fishery product technology</t>
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-9695-9333</t>
-        </is>
-      </c>
+      <c r="J24" s="12" t="n"/>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>6933123</t>
+          <t>6679664</t>
         </is>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>57221378035</t>
+          <t>57201354036</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr">
@@ -1717,12 +1713,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Badraeni, MP.</t>
+          <t>Mufti Hatur Rahmi, S.Tr.Pi., M.Si.</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1732,7 +1728,7 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Macro and Microalgae cultivation</t>
+          <t>Aquatic Product Technology</t>
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
@@ -1741,17 +1737,17 @@
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3762-6333</t>
+          <t>0000-0002-9695-9333</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>https://sinta.kemdikbud.go.id/authors/?q=badraeni</t>
+          <t>6933123</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>57192374833</t>
+          <t>57221378035</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
@@ -1764,18 +1760,50 @@
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="11" t="n"/>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Dr. Ir. Badraeni, MP.</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Macro and Microalgae cultivation</t>
+        </is>
+      </c>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="12" t="n"/>
       <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-3762-6333</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdikbud.go.id/authors/?q=badraeni</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>57192374833</t>
+        </is>
+      </c>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1964,15 +1992,32 @@
       <c r="L37" s="12" t="n"/>
       <c r="M37" s="12" t="n"/>
     </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
